--- a/final/Siruk-hx-303-prices-cat.xlsx
+++ b/final/Siruk-hx-303-prices-cat.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4150</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="23">
@@ -1056,6 +1056,26 @@
       </c>
       <c r="D32" t="n">
         <v>6000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Կեր կատուների Pro Plan Sterilised Adult Renal Plus, հնդկահավ, 10 կգ</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pro Plan Sterilised Adult Renal Plus — Turkey 10 kg</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>00106</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3950</v>
       </c>
     </row>
   </sheetData>
